--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_deviation_monitoring/deviation_monitoring/dsas_g11_bearings_vibration_temp_deviation_monitoring_output5.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_deviation_monitoring/deviation_monitoring/dsas_g11_bearings_vibration_temp_deviation_monitoring_output5.xlsx
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.0001338162943117333</v>
+        <v>0.0003883488850024687</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000404630165306163</v>
+        <v>0.0002940247927209409</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.0002251515962001258</v>
+        <v>0.0001395128372535255</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003866823083955593</v>
+        <v>0.0002785735971741993</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.0001865906151421808</v>
+        <v>0.0001323477696803605</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003666731390702214</v>
+        <v>0.0002639510144248154</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.0001865906151421808</v>
+        <v>0.0001323477696803605</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003486648866774172</v>
+        <v>0.0002507906899503699</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.0001865906151421808</v>
+        <v>0.0001323477696803605</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0003324574595238936</v>
+        <v>0.0002389463979233689</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.0001327431169698257</v>
+        <v>7.821629487273839e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003124860252684868</v>
+        <v>0.0002228733876183058</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.0008088133420245402</v>
+        <v>0.0003586265370189814</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0003621187569440921</v>
+        <v>0.0002364487025583734</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.0005666976699215856</v>
+        <v>0.0002773641812088329</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0003825766482418415</v>
+        <v>0.0002405402504234194</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>9.879012658057937e-05</v>
+        <v>0.000165361892263711</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0003541979960757152</v>
+        <v>0.0002330224146074485</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.0002480964932522363</v>
+        <v>0.0001160634611578797</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0003435878457933674</v>
+        <v>0.0002213265192624916</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.0002644615523041711</v>
+        <v>0.0002016412630333783</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0003356752164444477</v>
+        <v>0.0002193579936395803</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.000144598425676792</v>
+        <v>0.0001462508603679314</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0003165675373676822</v>
+        <v>0.0002120472803124154</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8.379415746433838e-05</v>
+        <v>0.000215516673358337</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0002932901993773478</v>
+        <v>0.0002123942196170076</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.496707923556397e-05</v>
+        <v>0.0002584843841527713</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0002714578873631693</v>
+        <v>0.000217003236070584</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.0005095614111921201</v>
+        <v>0.0001283124703154859</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0002952682397460644</v>
+        <v>0.0002081341594950742</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.0004869462676166437</v>
+        <v>0.0001342048257814718</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0003144360425331224</v>
+        <v>0.0002007412261237139</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.0004168763229004987</v>
+        <v>0.0001367129991691225</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0003246800705698601</v>
+        <v>0.0001943384034282548</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.0006185990306900581</v>
+        <v>0.0004200284653348239</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0003540719665818799</v>
+        <v>0.0002169074096189117</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.0004268031661954386</v>
+        <v>0.0002045771618666057</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0003613450865432357</v>
+        <v>0.0002156743848436811</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.0005016613215015579</v>
+        <v>0.0002311650422206513</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.000375376710039068</v>
+        <v>0.0002172234505813781</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.0007879452032384879</v>
+        <v>0.0003630762564741722</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.00041663355935901</v>
+        <v>0.0002318087311706575</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.0003530659113098465</v>
+        <v>0.0003933127039839389</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0004102767945540936</v>
+        <v>0.0002479591284519857</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.0006126020456970051</v>
+        <v>0.0002883356842767578</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0004305093196683848</v>
+        <v>0.0002519967840344629</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.0006649205381494051</v>
+        <v>0.0001099241621601146</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0004539504415164868</v>
+        <v>0.000237789521847028</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.0005141277551722459</v>
+        <v>0.0001923994228630433</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0004599681728820627</v>
+        <v>0.0002332505119486296</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.0005141277551722459</v>
+        <v>0.0001923994228630433</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.000465384131111081</v>
+        <v>0.0002291654030400709</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>6.631408335353568e-05</v>
+        <v>0.0001751628713737544</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0004254771263353264</v>
+        <v>0.0002237651498734393</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>8.829935551075933e-05</v>
+        <v>0.0001698683801365866</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0003917593492528697</v>
+        <v>0.0002183754728997541</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.0001040470570658028</v>
+        <v>0.0001755759154542516</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.000362988120034163</v>
+        <v>0.0002140955171552038</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.0001866956146327213</v>
+        <v>0.0003092119405388269</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0003453588694940189</v>
+        <v>0.0002236071594935662</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.000218553946833879</v>
+        <v>0.0002572923056392711</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0003326783772280049</v>
+        <v>0.0002269756741081366</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.0002271892293203494</v>
+        <v>0.0002415155898359306</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0003221294624372393</v>
+        <v>0.000228429665680916</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.0001345261212164825</v>
+        <v>0.0001611298260824856</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0003033691283151636</v>
+        <v>0.000221699681721073</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.0001652839981857376</v>
+        <v>0.0001531497975836959</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.000289560615302221</v>
+        <v>0.0002148446933073353</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.0001409745878921759</v>
+        <v>0.0001583598051883977</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0002747020125612164</v>
+        <v>0.0002091962044954415</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.0002090067520050412</v>
+        <v>0.0001634873545676708</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0002681324865055989</v>
+        <v>0.0002046253195026645</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.0001999352078006372</v>
+        <v>0.000213052198195864</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0002613127586351027</v>
+        <v>0.0002054680073719844</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.000143254159846745</v>
+        <v>0.0001273104245579247</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0002495068987562669</v>
+        <v>0.0001976522490905784</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.0001440369291620733</v>
+        <v>0.0002464620285658806</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0002389599017968476</v>
+        <v>0.0002025332270381086</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.0001628750841783221</v>
+        <v>0.0002515725840645488</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.000231351420034995</v>
+        <v>0.0002074371627407526</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.0001364392860668087</v>
+        <v>0.0001941798456524137</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.0002218602066381764</v>
+        <v>0.0002061114310319187</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.0001872100589243528</v>
+        <v>0.0002529191799194646</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.000218395191866794</v>
+        <v>0.0002107922059206733</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.0003680063598334967</v>
+        <v>0.0002312801081572575</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0002333563086634643</v>
+        <v>0.0002128409961443317</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.0002128133288610447</v>
+        <v>0.0001480290562739891</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0002313020106832223</v>
+        <v>0.0002063598021572974</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.0001236164295261815</v>
+        <v>0.0002281167999664862</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0002205334525675183</v>
+        <v>0.0002085355019382163</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.0001348156371265736</v>
+        <v>0.0001898890863060457</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0002119616710234238</v>
+        <v>0.0002066708603749992</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.0001989200423790002</v>
+        <v>0.0002574158661743324</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.0002106575081589814</v>
+        <v>0.0002117453609549325</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.0007206452708376426</v>
+        <v>0.0001377953172718138</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.0002616562844268476</v>
+        <v>0.0002043503565866206</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.0001703748913582724</v>
+        <v>0.0001406821877962176</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.00025252814511999</v>
+        <v>0.0001979835397075803</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.0001772620649662735</v>
+        <v>0.0001436210729772048</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0002450015371046184</v>
+        <v>0.0001925472930345428</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.0001311145818732739</v>
+        <v>0.0001611403598181239</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0002336128415814839</v>
+        <v>0.0001894065997129008</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.0002607909283448348</v>
+        <v>0.0001452109963309717</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.000236330650257819</v>
+        <v>0.0001849870393747079</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.0003214744003016394</v>
+        <v>0.0001362334364816893</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.0002448450252622011</v>
+        <v>0.0001801116790854061</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.0002229346994455883</v>
+        <v>0.0001748807914466099</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0002426539926805399</v>
+        <v>0.0001795885903215264</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.0002605330600639546</v>
+        <v>0.0001922040042698657</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.0002444418994188813</v>
+        <v>0.0001808501317163604</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.0002605330600639546</v>
+        <v>0.0001922040042698657</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.0002460510154833886</v>
+        <v>0.0001819855189717109</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.0002193294406705591</v>
+        <v>0.0002156395336314345</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.0002433788580021057</v>
+        <v>0.0001853509204376832</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.0001741358142437428</v>
+        <v>0.0001632490571687761</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0002364545536262694</v>
+        <v>0.0001831407341107925</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.0003167131105815531</v>
+        <v>0.0001545920142602467</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0002444804093217977</v>
+        <v>0.0001802858621257379</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.001485200485739296</v>
+        <v>0.0009088035079268421</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.0003685524169635476</v>
+        <v>0.0002531376267058484</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.0008354919078402786</v>
+        <v>0.0004171747714807739</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0004152463660512207</v>
+        <v>0.000269541341183341</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -4233,14 +4233,14 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.07778289478586869</v>
+        <v>0.001839256045237393</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.008152011208032972</v>
+        <v>0.0004265128115887462</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4293,14 +4293,14 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.0001713645423684312</v>
+        <v>0.0001363933452946616</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.007353946541466518</v>
+        <v>0.0003975008649593378</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4353,14 +4353,14 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.0001802459473284561</v>
+        <v>0.0001333325399788648</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.006636576482052712</v>
+        <v>0.0003710840324612905</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4413,14 +4413,14 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.000640116740303467</v>
+        <v>0.000156087176144465</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.006036930507877787</v>
+        <v>0.000349584346829608</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4473,14 +4473,14 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.001849916597322204</v>
+        <v>0.001589679617892744</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.005618229116822229</v>
+        <v>0.0004735938739359215</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4533,14 +4533,14 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.0008351589852560811</v>
+        <v>0.0002084689397633267</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.005139922103665614</v>
+        <v>0.0004470813805186621</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4593,14 +4593,14 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.0001457689180902431</v>
+        <v>0.0001486745104930764</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.004640506785108077</v>
+        <v>0.0004172406935161035</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4653,14 +4653,14 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.0001633203174005534</v>
+        <v>0.0001824034854207773</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.004192788138337324</v>
+        <v>0.0003937569727065709</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4713,14 +4713,14 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.0001912515006996406</v>
+        <v>0.0002100257785161913</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.003792634474573555</v>
+        <v>0.0003753838532875329</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4773,14 +4773,14 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.00016857090816728</v>
+        <v>0.0002171835538181398</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.003430228117932927</v>
+        <v>0.0003595638233405936</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4833,14 +4833,14 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.0008080140460692308</v>
+        <v>0.0003046899386855954</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.003168006710746557</v>
+        <v>0.0003540764348750938</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4893,14 +4893,14 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.0009868352836621189</v>
+        <v>0.0003206223661328556</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.002949889568038113</v>
+        <v>0.00035073102800087</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.0006606747369493176</v>
+        <v>0.00022187898148376</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.002720968084929233</v>
+        <v>0.000337845823349159</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.0008632032777719512</v>
+        <v>0.0001924587838206263</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002535191604213505</v>
+        <v>0.0003233071193963058</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.0002008923743703173</v>
+        <v>0.0001811725268386951</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002301761681229186</v>
+        <v>0.0003090936601405447</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.0001508310815960187</v>
+        <v>0.0001910727540766057</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.002086668621265869</v>
+        <v>0.0002972915695341508</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.0001599110818885648</v>
+        <v>0.0001680141359923935</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001893992867328138</v>
+        <v>0.0002843638261799751</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.0002269672429224086</v>
+        <v>0.0001924842202203304</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.001727290304887565</v>
+        <v>0.0002751758655840106</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.0001313029956671856</v>
+        <v>0.0001575106045905395</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001567691573965527</v>
+        <v>0.0002634093394846635</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.0001482594493532129</v>
+        <v>0.0001313577242199435</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001425748361504295</v>
+        <v>0.0002502041779581915</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.0001363898217687691</v>
+        <v>0.0002031457332442435</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.001296812507530743</v>
+        <v>0.0002454983334867967</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0.0001919936029275635</v>
+        <v>0.0001823493347584562</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001186330617070425</v>
+        <v>0.0002391834336139626</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.0002018738709997321</v>
+        <v>0.0002043816479602905</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001087884942463355</v>
+        <v>0.0002357032550485954</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.0003145291900095066</v>
+        <v>0.0004485727103374965</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.00101054936721797</v>
+        <v>0.0002569902005774855</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.009625746866977421</v>
+        <v>0.01092014795261731</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.001872069117193916</v>
+        <v>0.001323305975781469</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.0001204862698065704</v>
+        <v>0.0002415800442880183</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.001696910832455181</v>
+        <v>0.001215133382632123</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.0001204862698065704</v>
+        <v>0.0002415800442880183</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.00153926837619032</v>
+        <v>0.001117778048797713</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.0003102966829381579</v>
+        <v>0.0002215985835029478</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.001416371206865104</v>
+        <v>0.001028160102268236</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.0003645016248362837</v>
+        <v>0.0002669354150903394</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.001311184248662221</v>
+        <v>0.0009520376335504467</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.0003788433549639169</v>
+        <v>0.0002947580249157576</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.001217950159292391</v>
+        <v>0.0008863096726869778</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.0002238330082024666</v>
+        <v>0.0002573361569465672</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.001118538444183398</v>
+        <v>0.0008234123211129367</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.0001084249143904435</v>
+        <v>0.0001592418023542747</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.001017527091204103</v>
+        <v>0.0007569952692370705</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.0002738934163101815</v>
+        <v>0.0001961713179993714</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0009431637237147106</v>
+        <v>0.0007009128741133006</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.0002244941291440106</v>
+        <v>0.0001930338777093308</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.0008712967642576405</v>
+        <v>0.0006501249744729036</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.001151753619078666</v>
+        <v>0.0002635285689801255</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.0008993424497397432</v>
+        <v>0.0006114653339236258</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.0007369730738375539</v>
+        <v>0.0002555732621746241</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.0008831055121495243</v>
+        <v>0.0005758761267487256</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.0007467146582674879</v>
+        <v>0.000217654946897779</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.0008694664267613207</v>
+        <v>0.0005400540087636309</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.0009080389834414765</v>
+        <v>0.0001799515672474317</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.0008733236824293362</v>
+        <v>0.0005040437646120109</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.0009080389834414765</v>
+        <v>0.0001799515672474317</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.0008767952125305502</v>
+        <v>0.000471634544875553</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.0006391909476470757</v>
+        <v>0.0001441419114495077</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.0008530347860422027</v>
+        <v>0.0004388852815329484</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.0007830276850281321</v>
+        <v>0.0002247227570889959</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.0008460340759407956</v>
+        <v>0.0004174690290885531</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.0007830276850281321</v>
+        <v>0.0002247227570889959</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.0008397334368495292</v>
+        <v>0.0003981944018885974</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.0006551669958920996</v>
+        <v>0.0001162165258332257</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.0008212767927537862</v>
+        <v>0.0003699966142830602</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0.0005920394318625542</v>
+        <v>8.786698331337867e-05</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.0007983530566646631</v>
+        <v>0.000341783651186092</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0.0006146862826955689</v>
+        <v>0.0001591750494048068</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.0007799863792677537</v>
+        <v>0.0003235227910079635</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0.0007023387323427952</v>
+        <v>0.0001887893898228775</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.0007722216145752579</v>
+        <v>0.0003100494508894549</v>
       </c>
       <c r="R108" t="inlineStr">
         <is>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0.0006551632651293131</v>
+        <v>0.000224319924442749</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.0007605157796306633</v>
+        <v>0.0003014764982447843</v>
       </c>
       <c r="R109" t="inlineStr">
         <is>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0.0005220671319045628</v>
+        <v>0.000317490785364293</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.0007366709148580533</v>
+        <v>0.0003030779269567352</v>
       </c>
       <c r="R110" t="inlineStr">
         <is>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0.0001408887852396275</v>
+        <v>0.0001610561232148509</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.0006770927018962107</v>
+        <v>0.0002888757465825467</v>
       </c>
       <c r="R111" t="inlineStr">
         <is>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0.0004544791073804445</v>
+        <v>0.0001020838924541777</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.000654831342444634</v>
+        <v>0.0002701965611697098</v>
       </c>
       <c r="R112" t="inlineStr">
         <is>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0.0007620915440476607</v>
+        <v>0.0002731916161100747</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.0006655573626049366</v>
+        <v>0.0002704960666637463</v>
       </c>
       <c r="R113" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0.0005983552097355954</v>
+        <v>0.0001195394562340212</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.0006588371473180024</v>
+        <v>0.0002554004056207737</v>
       </c>
       <c r="R114" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0.0005002513295829773</v>
+        <v>0.0004524980188859954</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.0006429785655444999</v>
+        <v>0.0002751101669472959</v>
       </c>
       <c r="R115" t="inlineStr">
         <is>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0.0003239217997450303</v>
+        <v>0.0001576177798221065</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.000611072888964553</v>
+        <v>0.0002633609282347769</v>
       </c>
       <c r="R116" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0.0001987482708396394</v>
+        <v>0.0001874718580864165</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.0005698404271520615</v>
+        <v>0.0002557720212199409</v>
       </c>
       <c r="R117" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0.0005331343298520777</v>
+        <v>0.0001891997336396922</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.0005661698174220632</v>
+        <v>0.000249114792461916</v>
       </c>
       <c r="R118" t="inlineStr">
         <is>
@@ -7593,10 +7593,10 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0.0003480527588779582</v>
+        <v>0.0001242192972578346</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.0005443581115676528</v>
+        <v>0.0002366252429415079</v>
       </c>
       <c r="R119" t="inlineStr">
         <is>
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0.0002508682398699431</v>
+        <v>0.0002135426996707197</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.0005150091243978818</v>
+        <v>0.000234316988614429</v>
       </c>
       <c r="R120" t="inlineStr">
         <is>
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0.0009417247800008072</v>
+        <v>0.000244766989461975</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.0005576806899581744</v>
+        <v>0.0002353619886991836</v>
       </c>
       <c r="R121" t="inlineStr">
         <is>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0.001021166312659923</v>
+        <v>0.005654424930258558</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.0006040292522283493</v>
+        <v>0.0007772682828551213</v>
       </c>
       <c r="R122" t="inlineStr">
         <is>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0.0001898889475564965</v>
+        <v>0.0001656228157140964</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.0005626152217611639</v>
+        <v>0.0007161037361410189</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0.0002464336188197631</v>
+        <v>0.0001649120457967381</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.0005309970614670238</v>
+        <v>0.0006609845671065908</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
@@ -7953,10 +7953,10 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0.0004329933560497237</v>
+        <v>0.0001095255865903967</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.0005211966909252938</v>
+        <v>0.0006058386690549714</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0.0003434123695248183</v>
+        <v>8.014054076494898e-05</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.0005034182587852462</v>
+        <v>0.0005532688562259691</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0.0001653401087173544</v>
+        <v>0.0001494060711070553</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.000469610443778457</v>
+        <v>0.0005128825777140777</v>
       </c>
       <c r="R127" t="inlineStr">
         <is>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0.0001653401087173544</v>
+        <v>0.0001494060711070553</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.0004391834102723467</v>
+        <v>0.0004765349270533754</v>
       </c>
       <c r="R128" t="inlineStr">
         <is>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0.0002047779641770661</v>
+        <v>0.000216149779719914</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.0004157428656628186</v>
+        <v>0.0004504964123200293</v>
       </c>
       <c r="R129" t="inlineStr">
         <is>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0.0002842554008212304</v>
+        <v>0.0001678644124362507</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.0004025941191786598</v>
+        <v>0.0004222332123316513</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0.0003232206546446962</v>
+        <v>0.0001752902124197369</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.0003946567727252635</v>
+        <v>0.0003975389123404599</v>
       </c>
       <c r="R131" t="inlineStr">
         <is>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0.0002447453055048191</v>
+        <v>0.0001724432388044533</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.0003796656260032191</v>
+        <v>0.0003750293449868592</v>
       </c>
       <c r="R132" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0.0001656155585588718</v>
+        <v>0.0002064671745171947</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.0003582606192587844</v>
+        <v>0.0003581731279398927</v>
       </c>
       <c r="R133" t="inlineStr">
         <is>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0.0002236759514837121</v>
+        <v>0.0002734207179079274</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.0003448021524812771</v>
+        <v>0.0003496978869366962</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0.003362863381298886</v>
+        <v>0.005488221880834074</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.0006466082753630382</v>
+        <v>0.0008635502863264343</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0.0001128727698198456</v>
+        <v>0.0001554012260746175</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.0005932347248087189</v>
+        <v>0.0007927353803012525</v>
       </c>
       <c r="R136" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0.0007402768837671874</v>
+        <v>0.0002032862817149464</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.0006079389407045657</v>
+        <v>0.0007337904704426218</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0.0008919799121890697</v>
+        <v>0.0001791891623375131</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.0006363430378530162</v>
+        <v>0.0006783303396321109</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0.0007854961410167071</v>
+        <v>0.0001861324200014054</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.0006512583481693853</v>
+        <v>0.0006291105476690404</v>
       </c>
       <c r="R139" t="inlineStr">
         <is>
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0.0005746277271112662</v>
+        <v>0.0001622116897805442</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.0006435952860635734</v>
+        <v>0.0005824206618801908</v>
       </c>
       <c r="R140" t="inlineStr">
         <is>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0.0007662840680572371</v>
+        <v>0.0001491602263957801</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.0006558641642629398</v>
+        <v>0.0005390946183317498</v>
       </c>
       <c r="R141" t="inlineStr">
         <is>
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0.0005681776212087103</v>
+        <v>0.0001916452834128994</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.0006470955099575168</v>
+        <v>0.0005043496848398648</v>
       </c>
       <c r="R142" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0.0007350698751364859</v>
+        <v>0.0001493636785070418</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.0006558929464754138</v>
+        <v>0.0004688510842065825</v>
       </c>
       <c r="R143" t="inlineStr">
         <is>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0.000857639458792066</v>
+        <v>8.564276655279146e-05</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.0006760675977070791</v>
+        <v>0.0004305302524412033</v>
       </c>
       <c r="R144" t="inlineStr">
         <is>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0.0007867262613341878</v>
+        <v>0.0001139142749257257</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.0006871334640697899</v>
+        <v>0.0003988686546896555</v>
       </c>
       <c r="R145" t="inlineStr">
         <is>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0.001025750817972021</v>
+        <v>0.0001717413934221558</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.0007209951994600131</v>
+        <v>0.0003761559285629056</v>
       </c>
       <c r="R146" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0.0006992068966437793</v>
+        <v>0.0003371625322197767</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.0007188163691783897</v>
+        <v>0.0003722565889285927</v>
       </c>
       <c r="R147" t="inlineStr">
         <is>
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0.0008935734913936903</v>
+        <v>0.0001370136355973214</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.0007362920813999197</v>
+        <v>0.0003487322935954656</v>
       </c>
       <c r="R148" t="inlineStr">
         <is>
@@ -9393,10 +9393,10 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0.0008541210176548204</v>
+        <v>0.0001785057477017719</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.0007480749750254099</v>
+        <v>0.0003317096390060962</v>
       </c>
       <c r="R149" t="inlineStr">
         <is>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0.01223411042216235</v>
+        <v>0.008976728862481855</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.001896678519739105</v>
+        <v>0.001196211561353673</v>
       </c>
       <c r="R150" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0.0009001687786132759</v>
+        <v>0.0002280536278852456</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.001797027545626522</v>
+        <v>0.00109939576800683</v>
       </c>
       <c r="R151" t="inlineStr">
         <is>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0.001465941780666577</v>
+        <v>0.0003276510615259848</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.001763918969130527</v>
+        <v>0.001022221297358745</v>
       </c>
       <c r="R152" t="inlineStr">
         <is>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0.0008018842582684812</v>
+        <v>0.0001982825425286739</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.001667715498044323</v>
+        <v>0.0009398274218757382</v>
       </c>
       <c r="R153" t="inlineStr">
         <is>
